--- a/FORMULARIO/PRUEBA2.xlsx
+++ b/FORMULARIO/PRUEBA2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Documents\JUAN\BYDE\2025\COMISIÓN JORNADAS INTEGRADAS 2025\POSTERS_JIA_FCAUNJU_2025\FORMULARIO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6D6AFAC-A7A4-4572-9557-C44D65B72112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AC3FBBA-4AB9-4FF1-BADC-2395767A1A4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,9 +52,6 @@
     <t>Vera, M.L:; Alabar, F.D.</t>
   </si>
   <si>
-    <t>micorreo@fca.unju.edu.ar</t>
-  </si>
-  <si>
     <t>https://drive.google.com/open?id=11wYL8FDY_U-sqcSTYp00Q3jwqnvHoZM2</t>
   </si>
   <si>
@@ -83,6 +80,9 @@
   </si>
   <si>
     <t>Diversidad de Bacterias Endófitas Cultivables Asociadas a Plantas de Arándano</t>
+  </si>
+  <si>
+    <t>davidalabar@hotmail.com</t>
   </si>
 </sst>
 </file>
@@ -671,10 +671,10 @@
         <v>8</v>
       </c>
       <c r="E2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>9</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -682,19 +682,19 @@
         <v>45900.504151527777</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="8" t="s">
+      <c r="E3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="F3" s="9" t="s">
         <v>13</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -702,19 +702,19 @@
         <v>45900.505460787041</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="E4" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="F4" s="12" t="s">
         <v>17</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
